--- a/02_Pipeline/outputs/timeline_view.xlsx
+++ b/02_Pipeline/outputs/timeline_view.xlsx
@@ -550,7 +550,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>['Academic Lecturer', 'Biologist', 'Data Scientist', 'Education']</t>
+          <t>['Biologist', 'Data Scientist', 'Education']</t>
         </is>
       </c>
     </row>

--- a/02_Pipeline/outputs/timeline_view.xlsx
+++ b/02_Pipeline/outputs/timeline_view.xlsx
@@ -550,7 +550,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>['Biologist', 'Data Scientist', 'Education']</t>
+          <t>['Academic Lecturer', 'Biologist', 'Data Scientist', 'Education']</t>
         </is>
       </c>
     </row>
